--- a/public/formsExcelTemplates/Anamnesis.xlsx
+++ b/public/formsExcelTemplates/Anamnesis.xlsx
@@ -193,7 +193,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="16">
+  <borders count="17">
     <border>
       <left style="none"/>
       <right style="none"/>
@@ -316,67 +316,80 @@
       <top style="thin">
         <color auto="1"/>
       </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
       <diagonal style="none"/>
     </border>
     <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
       <left style="thin">
         <color auto="1"/>
       </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="none"/>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
       <right style="medium">
         <color auto="1"/>
       </right>
       <top style="thin">
         <color auto="1"/>
       </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
       <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
         <color auto="1"/>
       </bottom>
       <diagonal style="none"/>
@@ -424,7 +437,7 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="1" fillId="0" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -471,13 +484,16 @@
     <xf fontId="0" fillId="0" borderId="3" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="2" fillId="0" borderId="13" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf fontId="0" fillId="0" borderId="13" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf fontId="2" fillId="0" borderId="14" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf fontId="2" fillId="0" borderId="15" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf fontId="2" fillId="0" borderId="16" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1068,49 +1084,49 @@
     </row>
     <row r="7">
       <c r="A7" s="7"/>
-      <c r="B7" s="8" t="s">
+      <c r="B7" s="16" t="s">
         <v>11</v>
       </c>
       <c r="C7" s="9"/>
     </row>
     <row r="8">
       <c r="A8" s="7"/>
-      <c r="B8" s="8" t="s">
+      <c r="B8" s="16" t="s">
         <v>12</v>
       </c>
       <c r="C8" s="9"/>
     </row>
     <row r="9">
       <c r="A9" s="7"/>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="16" t="s">
         <v>13</v>
       </c>
       <c r="C9" s="9"/>
     </row>
     <row r="10">
       <c r="A10" s="7"/>
-      <c r="B10" s="8" t="s">
+      <c r="B10" s="16" t="s">
         <v>14</v>
       </c>
       <c r="C10" s="9"/>
     </row>
     <row r="11">
       <c r="A11" s="7"/>
-      <c r="B11" s="8" t="s">
+      <c r="B11" s="16" t="s">
         <v>15</v>
       </c>
       <c r="C11" s="9"/>
     </row>
     <row r="12">
       <c r="A12" s="7"/>
-      <c r="B12" s="8" t="s">
+      <c r="B12" s="16" t="s">
         <v>16</v>
       </c>
       <c r="C12" s="9"/>
     </row>
     <row r="13" ht="15">
       <c r="A13" s="10"/>
-      <c r="B13" s="11" t="s">
+      <c r="B13" s="8" t="s">
         <v>17</v>
       </c>
       <c r="C13" s="12"/>
@@ -1126,21 +1142,21 @@
     </row>
     <row r="15">
       <c r="A15" s="7"/>
-      <c r="B15" s="8" t="s">
+      <c r="B15" s="16" t="s">
         <v>20</v>
       </c>
       <c r="C15" s="9"/>
     </row>
     <row r="16">
       <c r="A16" s="7"/>
-      <c r="B16" s="8" t="s">
+      <c r="B16" s="16" t="s">
         <v>21</v>
       </c>
       <c r="C16" s="9"/>
     </row>
     <row r="17" ht="15">
       <c r="A17" s="10"/>
-      <c r="B17" s="11" t="s">
+      <c r="B17" s="8" t="s">
         <v>22</v>
       </c>
       <c r="C17" s="12"/>
@@ -1156,56 +1172,56 @@
     </row>
     <row r="19">
       <c r="A19" s="7"/>
-      <c r="B19" s="8" t="s">
+      <c r="B19" s="16" t="s">
         <v>25</v>
       </c>
       <c r="C19" s="9"/>
     </row>
     <row r="20">
       <c r="A20" s="7"/>
-      <c r="B20" s="8" t="s">
+      <c r="B20" s="16" t="s">
         <v>26</v>
       </c>
       <c r="C20" s="9"/>
     </row>
     <row r="21">
       <c r="A21" s="7"/>
-      <c r="B21" s="8" t="s">
+      <c r="B21" s="16" t="s">
         <v>27</v>
       </c>
       <c r="C21" s="9"/>
     </row>
     <row r="22">
       <c r="A22" s="7"/>
-      <c r="B22" s="8" t="s">
+      <c r="B22" s="16" t="s">
         <v>28</v>
       </c>
       <c r="C22" s="9"/>
     </row>
     <row r="23">
       <c r="A23" s="7"/>
-      <c r="B23" s="8" t="s">
+      <c r="B23" s="16" t="s">
         <v>29</v>
       </c>
       <c r="C23" s="9"/>
     </row>
     <row r="24">
       <c r="A24" s="7"/>
-      <c r="B24" s="8" t="s">
+      <c r="B24" s="16" t="s">
         <v>30</v>
       </c>
       <c r="C24" s="9"/>
     </row>
     <row r="25">
       <c r="A25" s="7"/>
-      <c r="B25" s="8" t="s">
+      <c r="B25" s="16" t="s">
         <v>31</v>
       </c>
       <c r="C25" s="9"/>
     </row>
     <row r="26" ht="15">
       <c r="A26" s="10"/>
-      <c r="B26" s="11" t="s">
+      <c r="B26" s="8" t="s">
         <v>32</v>
       </c>
       <c r="C26" s="12"/>
@@ -1221,35 +1237,35 @@
     </row>
     <row r="28">
       <c r="A28" s="7"/>
-      <c r="B28" s="8" t="s">
+      <c r="B28" s="16" t="s">
         <v>35</v>
       </c>
       <c r="C28" s="9"/>
     </row>
     <row r="29">
       <c r="A29" s="7"/>
-      <c r="B29" s="8" t="s">
+      <c r="B29" s="16" t="s">
         <v>36</v>
       </c>
       <c r="C29" s="9"/>
     </row>
     <row r="30">
       <c r="A30" s="7"/>
-      <c r="B30" s="8" t="s">
+      <c r="B30" s="16" t="s">
         <v>37</v>
       </c>
       <c r="C30" s="9"/>
     </row>
     <row r="31">
       <c r="A31" s="7"/>
-      <c r="B31" s="8" t="s">
+      <c r="B31" s="16" t="s">
         <v>38</v>
       </c>
       <c r="C31" s="9"/>
     </row>
     <row r="32" ht="15">
       <c r="A32" s="10"/>
-      <c r="B32" s="11" t="s">
+      <c r="B32" s="8" t="s">
         <v>39</v>
       </c>
       <c r="C32" s="12"/>
@@ -1265,7 +1281,7 @@
     </row>
     <row r="34" ht="15">
       <c r="A34" s="10"/>
-      <c r="B34" s="11" t="s">
+      <c r="B34" s="8" t="s">
         <v>42</v>
       </c>
       <c r="C34" s="12"/>
@@ -1281,17 +1297,17 @@
     </row>
     <row r="36" ht="15">
       <c r="A36" s="10"/>
-      <c r="B36" s="11" t="s">
+      <c r="B36" s="8" t="s">
         <v>45</v>
       </c>
       <c r="C36" s="12"/>
     </row>
     <row r="37" ht="15">
-      <c r="A37" s="16" t="s">
+      <c r="A37" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="B37" s="17"/>
-      <c r="C37" s="18"/>
+      <c r="B37" s="18"/>
+      <c r="C37" s="19"/>
     </row>
   </sheetData>
   <mergeCells count="8">
